--- a/data/trans_orig/Q5407-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>22262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>18944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272104</t>
+          <t>271860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285445</t>
+          <t>285906</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>300300</t>
+          <t>301101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>321782</t>
+          <t>322064</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>579040</t>
+          <t>578407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>604586</t>
+          <t>603929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48156</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>46493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77444</t>
+          <t>76796</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74727</t>
+          <t>74604</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110205</t>
+          <t>110770</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160577</t>
+          <t>160470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181706</t>
+          <t>181977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229361</t>
+          <t>227554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261643</t>
+          <t>260969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394944</t>
+          <t>394224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>436621</t>
+          <t>436594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>55443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99345</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142200</t>
+          <t>141687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>437558</t>
+          <t>435923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462859</t>
+          <t>462814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>537481</t>
+          <t>535947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578079</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>985298</t>
+          <t>985709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1035390</t>
+          <t>1033098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>28390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55373</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>275370</t>
+          <t>273266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293924</t>
+          <t>293855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>295005</t>
+          <t>292788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>320869</t>
+          <t>320572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>576637</t>
+          <t>575838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>609949</t>
+          <t>608790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34682</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56814</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88039</t>
+          <t>87725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75540</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>57362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60839</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91781</t>
+          <t>93314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>98368</t>
+          <t>99497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141315</t>
+          <t>142530</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167234</t>
+          <t>167923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198394</t>
+          <t>199815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220988</t>
+          <t>222436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260624</t>
+          <t>261385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>401469</t>
+          <t>398326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449985</t>
+          <t>452350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73389</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108386</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101386</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>147138</t>
+          <t>147589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84986</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122128</t>
+          <t>124369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134633</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183096</t>
+          <t>182821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450990</t>
+          <t>449916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>487987</t>
+          <t>487638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524506</t>
+          <t>525941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>575007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>989582</t>
+          <t>988587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1050794</t>
+          <t>1050326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53231</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64205</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>303426</t>
+          <t>303191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>321332</t>
+          <t>321269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>314526</t>
+          <t>315866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>340819</t>
+          <t>341964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>625894</t>
+          <t>624971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>657598</t>
+          <t>657615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30168</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34296</t>
+          <t>34160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61859</t>
+          <t>63839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84920</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31247</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75093</t>
+          <t>75296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113452</t>
+          <t>114353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>116135</t>
+          <t>114896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>159914</t>
+          <t>157119</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181718</t>
+          <t>181786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206244</t>
+          <t>206647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>235957</t>
+          <t>237302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>280413</t>
+          <t>280631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>426151</t>
+          <t>428470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>479751</t>
+          <t>478921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>44076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>72594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68665</t>
+          <t>69643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109238</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65481</t>
+          <t>63121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114610</t>
+          <t>111568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160447</t>
+          <t>158653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160084</t>
+          <t>159991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212281</t>
+          <t>213256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490224</t>
+          <t>492349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524113</t>
+          <t>523682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>559428</t>
+          <t>562186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612118</t>
+          <t>614039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1063801</t>
+          <t>1065959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1126045</t>
+          <t>1126778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>35788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57148</t>
+          <t>62766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>51324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>76624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>338514</t>
+          <t>376098</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329756</t>
+          <t>366960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>345857</t>
+          <t>383864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>554728</t>
+          <t>379048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>523193</t>
+          <t>368593</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>587255</t>
+          <t>388410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>893243</t>
+          <t>755146</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>865010</t>
+          <t>740925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>934634</t>
+          <t>768509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607365</t>
+          <t>438126</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607365</t>
+          <t>438126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607365</t>
+          <t>438126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>975531</t>
+          <t>845206</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>975531</t>
+          <t>845206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>975531</t>
+          <t>845206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>81145</t>
+          <t>88713</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>76430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92449</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>118905</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>104936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124238</t>
+          <t>136747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>45789</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52258</t>
+          <t>56916</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>115966</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104029</t>
+          <t>112332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130561</t>
+          <t>141171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>158271</t>
+          <t>172157</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141573</t>
+          <t>154278</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>173743</t>
+          <t>190171</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>210227</t>
+          <t>232326</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>199107</t>
+          <t>219484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221610</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>226730</t>
+          <t>247744</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>213166</t>
+          <t>231874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241331</t>
+          <t>264293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>436958</t>
+          <t>480070</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>418578</t>
+          <t>460317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>456594</t>
+          <t>500263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281282</t>
+          <t>308307</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281282</t>
+          <t>308307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281282</t>
+          <t>308307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>423842</t>
+          <t>462825</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423842</t>
+          <t>462825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>423842</t>
+          <t>462825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>705125</t>
+          <t>771132</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>705125</t>
+          <t>771132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705125</t>
+          <t>771132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50537</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>95244</t>
+          <t>104621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>91211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124378</t>
+          <t>119105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>135036</t>
+          <t>146199</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87297</t>
+          <t>130743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160311</t>
+          <t>163636</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74595</t>
+          <t>79206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>154505</t>
+          <t>169538</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>152408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>198117</t>
+          <t>186730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>215419</t>
+          <t>234923</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139888</t>
+          <t>213735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252228</t>
+          <t>257702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>548742</t>
+          <t>608424</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>532550</t>
+          <t>591798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>562169</t>
+          <t>623513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>781459</t>
+          <t>626792</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712522</t>
+          <t>604134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885516</t>
+          <t>646744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1330200</t>
+          <t>1235216</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1272442</t>
+          <t>1208269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1458269</t>
+          <t>1259414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
